--- a/CHARMS REFLEXION.xlsx
+++ b/CHARMS REFLEXION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D6A21C-429A-462F-8F3B-24FB8C95497A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91E751-22E4-4232-BB32-B1EE47A23F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BAD9DA9B-3134-462C-8E65-661561964EA0}"/>
   </bookViews>
